--- a/artfynd/A 25794-2024 artfynd.xlsx
+++ b/artfynd/A 25794-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137369217</v>
       </c>
       <c r="B4" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137369240</v>
       </c>
       <c r="B5" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137369263</v>
       </c>
       <c r="B6" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137369233</v>
       </c>
       <c r="B7" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137369271</v>
       </c>
       <c r="B8" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137369219</v>
       </c>
       <c r="B9" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137369220</v>
       </c>
       <c r="B10" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137369229</v>
       </c>
       <c r="B11" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 25794-2024 artfynd.xlsx
+++ b/artfynd/A 25794-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137369216</v>
       </c>
       <c r="B2" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137369247</v>
       </c>
       <c r="B3" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137369217</v>
       </c>
       <c r="B4" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137369240</v>
       </c>
       <c r="B5" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137369263</v>
       </c>
       <c r="B6" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137369233</v>
       </c>
       <c r="B7" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137369271</v>
       </c>
       <c r="B8" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137369219</v>
       </c>
       <c r="B9" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137369220</v>
       </c>
       <c r="B10" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137369229</v>
       </c>
       <c r="B11" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137369218</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137369230</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137369238</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137369246</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137369232</v>
       </c>
       <c r="B16" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137369253</v>
       </c>
       <c r="B17" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137369261</v>
       </c>
       <c r="B18" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137369255</v>
       </c>
       <c r="B19" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137369221</v>
       </c>
       <c r="B20" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137369235</v>
       </c>
       <c r="B21" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137369237</v>
       </c>
       <c r="B22" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137369251</v>
       </c>
       <c r="B23" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137369264</v>
       </c>
       <c r="B24" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137369266</v>
       </c>
       <c r="B25" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137369262</v>
       </c>
       <c r="B26" t="n">
-        <v>78516</v>
+        <v>78521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137369239</v>
       </c>
       <c r="B27" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>137369236</v>
       </c>
       <c r="B28" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>137369250</v>
       </c>
       <c r="B29" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>137369252</v>
       </c>
       <c r="B30" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>137369259</v>
       </c>
       <c r="B31" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>137369260</v>
       </c>
       <c r="B32" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>137369223</v>
       </c>
       <c r="B33" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137369225</v>
       </c>
       <c r="B34" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137369227</v>
       </c>
       <c r="B35" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137369257</v>
       </c>
       <c r="B36" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137369267</v>
       </c>
       <c r="B37" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137369228</v>
       </c>
       <c r="B38" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137369249</v>
       </c>
       <c r="B39" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>137369234</v>
       </c>
       <c r="B40" t="n">
-        <v>80410</v>
+        <v>80415</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 25794-2024 artfynd.xlsx
+++ b/artfynd/A 25794-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137369216</v>
       </c>
       <c r="B2" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137369247</v>
       </c>
       <c r="B3" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137369217</v>
       </c>
       <c r="B4" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137369240</v>
       </c>
       <c r="B5" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137369263</v>
       </c>
       <c r="B6" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137369233</v>
       </c>
       <c r="B7" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137369271</v>
       </c>
       <c r="B8" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137369219</v>
       </c>
       <c r="B9" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137369220</v>
       </c>
       <c r="B10" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137369229</v>
       </c>
       <c r="B11" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137369218</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137369230</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137369238</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137369246</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137369232</v>
       </c>
       <c r="B16" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137369253</v>
       </c>
       <c r="B17" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137369261</v>
       </c>
       <c r="B18" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137369255</v>
       </c>
       <c r="B19" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137369221</v>
       </c>
       <c r="B20" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137369235</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137369237</v>
       </c>
       <c r="B22" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137369251</v>
       </c>
       <c r="B23" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137369264</v>
       </c>
       <c r="B24" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137369266</v>
       </c>
       <c r="B25" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137369262</v>
       </c>
       <c r="B26" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>137369236</v>
       </c>
       <c r="B28" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>137369250</v>
       </c>
       <c r="B29" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>137369252</v>
       </c>
       <c r="B30" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>137369259</v>
       </c>
       <c r="B31" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>137369260</v>
       </c>
       <c r="B32" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>137369223</v>
       </c>
       <c r="B33" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137369225</v>
       </c>
       <c r="B34" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137369227</v>
       </c>
       <c r="B35" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137369257</v>
       </c>
       <c r="B36" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137369267</v>
       </c>
       <c r="B37" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137369228</v>
       </c>
       <c r="B38" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137369249</v>
       </c>
       <c r="B39" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>137369234</v>
       </c>
       <c r="B40" t="n">
-        <v>80415</v>
+        <v>80426</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 25794-2024 artfynd.xlsx
+++ b/artfynd/A 25794-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137369216</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137369247</v>
       </c>
       <c r="B3" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137369217</v>
       </c>
       <c r="B4" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137369240</v>
       </c>
       <c r="B5" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137369263</v>
       </c>
       <c r="B6" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137369233</v>
       </c>
       <c r="B7" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137369271</v>
       </c>
       <c r="B8" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137369219</v>
       </c>
       <c r="B9" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137369220</v>
       </c>
       <c r="B10" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137369229</v>
       </c>
       <c r="B11" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137369218</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137369230</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137369238</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137369246</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137369232</v>
       </c>
       <c r="B16" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137369253</v>
       </c>
       <c r="B17" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137369261</v>
       </c>
       <c r="B18" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137369255</v>
       </c>
       <c r="B19" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137369221</v>
       </c>
       <c r="B20" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137369235</v>
       </c>
       <c r="B21" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137369237</v>
       </c>
       <c r="B22" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137369251</v>
       </c>
       <c r="B23" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137369264</v>
       </c>
       <c r="B24" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137369266</v>
       </c>
       <c r="B25" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137369262</v>
       </c>
       <c r="B26" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>137369236</v>
       </c>
       <c r="B28" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>137369250</v>
       </c>
       <c r="B29" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>137369252</v>
       </c>
       <c r="B30" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>137369259</v>
       </c>
       <c r="B31" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>137369260</v>
       </c>
       <c r="B32" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>137369223</v>
       </c>
       <c r="B33" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137369225</v>
       </c>
       <c r="B34" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137369227</v>
       </c>
       <c r="B35" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137369257</v>
       </c>
       <c r="B36" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137369267</v>
       </c>
       <c r="B37" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137369228</v>
       </c>
       <c r="B38" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137369249</v>
       </c>
       <c r="B39" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>137369234</v>
       </c>
       <c r="B40" t="n">
-        <v>80426</v>
+        <v>80427</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 25794-2024 artfynd.xlsx
+++ b/artfynd/A 25794-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137369216</v>
       </c>
       <c r="B2" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137369247</v>
       </c>
       <c r="B3" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137369217</v>
       </c>
       <c r="B4" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137369240</v>
       </c>
       <c r="B5" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137369263</v>
       </c>
       <c r="B6" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137369233</v>
       </c>
       <c r="B7" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137369271</v>
       </c>
       <c r="B8" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137369219</v>
       </c>
       <c r="B9" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137369220</v>
       </c>
       <c r="B10" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137369229</v>
       </c>
       <c r="B11" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137369218</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137369230</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137369238</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137369246</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137369232</v>
       </c>
       <c r="B16" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137369253</v>
       </c>
       <c r="B17" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137369261</v>
       </c>
       <c r="B18" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137369255</v>
       </c>
       <c r="B19" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137369221</v>
       </c>
       <c r="B20" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137369235</v>
       </c>
       <c r="B21" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137369237</v>
       </c>
       <c r="B22" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137369251</v>
       </c>
       <c r="B23" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137369264</v>
       </c>
       <c r="B24" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137369266</v>
       </c>
       <c r="B25" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137369262</v>
       </c>
       <c r="B26" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>137369236</v>
       </c>
       <c r="B28" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>137369250</v>
       </c>
       <c r="B29" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>137369252</v>
       </c>
       <c r="B30" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>137369259</v>
       </c>
       <c r="B31" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>137369260</v>
       </c>
       <c r="B32" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>137369223</v>
       </c>
       <c r="B33" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137369225</v>
       </c>
       <c r="B34" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137369227</v>
       </c>
       <c r="B35" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137369257</v>
       </c>
       <c r="B36" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137369267</v>
       </c>
       <c r="B37" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137369228</v>
       </c>
       <c r="B38" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137369249</v>
       </c>
       <c r="B39" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>137369234</v>
       </c>
       <c r="B40" t="n">
-        <v>80427</v>
+        <v>80429</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 25794-2024 artfynd.xlsx
+++ b/artfynd/A 25794-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137369216</v>
       </c>
       <c r="B2" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137369247</v>
       </c>
       <c r="B3" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137369217</v>
       </c>
       <c r="B4" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137369240</v>
       </c>
       <c r="B5" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137369263</v>
       </c>
       <c r="B6" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137369233</v>
       </c>
       <c r="B7" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137369271</v>
       </c>
       <c r="B8" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137369219</v>
       </c>
       <c r="B9" t="n">
-        <v>93489</v>
+        <v>93493</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137369220</v>
       </c>
       <c r="B10" t="n">
-        <v>93489</v>
+        <v>93493</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137369229</v>
       </c>
       <c r="B11" t="n">
-        <v>93489</v>
+        <v>93493</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137369218</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137369230</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137369238</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137369246</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137369232</v>
       </c>
       <c r="B16" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137369253</v>
       </c>
       <c r="B17" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137369261</v>
       </c>
       <c r="B18" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137369255</v>
       </c>
       <c r="B19" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137369221</v>
       </c>
       <c r="B20" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137369235</v>
       </c>
       <c r="B21" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137369237</v>
       </c>
       <c r="B22" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137369251</v>
       </c>
       <c r="B23" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137369264</v>
       </c>
       <c r="B24" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137369266</v>
       </c>
       <c r="B25" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137369262</v>
       </c>
       <c r="B26" t="n">
-        <v>78535</v>
+        <v>78539</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137369239</v>
       </c>
       <c r="B27" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>137369236</v>
       </c>
       <c r="B28" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>137369250</v>
       </c>
       <c r="B29" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>137369252</v>
       </c>
       <c r="B30" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>137369259</v>
       </c>
       <c r="B31" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>137369260</v>
       </c>
       <c r="B32" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>137369223</v>
       </c>
       <c r="B33" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137369225</v>
       </c>
       <c r="B34" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137369227</v>
       </c>
       <c r="B35" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137369257</v>
       </c>
       <c r="B36" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137369267</v>
       </c>
       <c r="B37" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137369228</v>
       </c>
       <c r="B38" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137369249</v>
       </c>
       <c r="B39" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>137369234</v>
       </c>
       <c r="B40" t="n">
-        <v>80429</v>
+        <v>80433</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
